--- a/Zeitplan-Aktuell-CNR4PQP(Automatisch wiederhergestellt).xlsx
+++ b/Zeitplan-Aktuell-CNR4PQP(Automatisch wiederhergestellt).xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\romes\Documents\MasterarbeitMax\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6298837f4a5fac96/Dokumente/Mafia/Masterarbeit/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B0A240EB-047F-44A5-A3DF-D21DF158630A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="411" documentId="8_{2267B131-370B-4ADA-B6DC-6C1D878C6B49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AEE91AD3-413A-4017-9EF5-C30ED60FD7F0}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" xr2:uid="{56F6048D-F352-49D9-A353-A3AAF0180454}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="490" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="451" uniqueCount="126">
   <si>
     <t>Bait</t>
   </si>
@@ -215,9 +215,6 @@
     <t>7</t>
   </si>
   <si>
-    <t>10-15</t>
-  </si>
-  <si>
     <t>10</t>
   </si>
   <si>
@@ -234,9 +231,6 @@
   </si>
   <si>
     <t>beschlagen</t>
-  </si>
-  <si>
-    <t>15</t>
   </si>
   <si>
     <t>Chole Nursery</t>
@@ -441,9 +435,6 @@
   </si>
   <si>
     <t>bei welcher analyse die größten unterschiede?</t>
-  </si>
-  <si>
-    <t>20</t>
   </si>
 </sst>
 </file>
@@ -537,7 +528,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -554,6 +545,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="2" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Link" xfId="1" builtinId="8"/>
@@ -897,7 +889,7 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.109375" customWidth="1"/>
-    <col min="10" max="10" width="10.88671875" style="4"/>
+    <col min="10" max="10" width="10.88671875" style="16"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:27" x14ac:dyDescent="0.3">
@@ -925,7 +917,7 @@
       <c r="I1" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="J1" s="16" t="s">
         <v>11</v>
       </c>
       <c r="K1" t="s">
@@ -941,7 +933,7 @@
         <v>23</v>
       </c>
       <c r="V1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.3">
@@ -972,7 +964,7 @@
       <c r="I3" s="4">
         <v>0</v>
       </c>
-      <c r="J3" s="4">
+      <c r="J3" s="16">
         <v>15</v>
       </c>
       <c r="K3" s="10" t="s">
@@ -985,7 +977,7 @@
         <v>10</v>
       </c>
       <c r="V3" s="11" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.3">
@@ -1002,7 +994,7 @@
         <v>14</v>
       </c>
       <c r="E4" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>15</v>
@@ -1016,7 +1008,7 @@
       <c r="I4" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="J4" s="4">
+      <c r="J4" s="16">
         <v>15</v>
       </c>
       <c r="K4" s="10" t="s">
@@ -1029,10 +1021,10 @@
         <v>8</v>
       </c>
       <c r="N4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="V4" s="11" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.3">
@@ -1063,7 +1055,7 @@
       <c r="I5" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="J5" s="4">
+      <c r="J5" s="16">
         <v>10</v>
       </c>
       <c r="K5" s="10" t="s">
@@ -1076,11 +1068,11 @@
         <v>10</v>
       </c>
       <c r="N5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="O5" s="3"/>
       <c r="V5" s="11" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AA5" t="s">
         <v>1</v>
@@ -1100,7 +1092,7 @@
         <v>14</v>
       </c>
       <c r="E6" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F6" s="4">
         <v>5</v>
@@ -1114,7 +1106,7 @@
       <c r="I6" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="J6" s="4">
+      <c r="J6" s="16">
         <v>10</v>
       </c>
       <c r="K6" s="10" t="s">
@@ -1127,10 +1119,10 @@
         <v>8</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="V6" s="11" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.3">
@@ -1147,7 +1139,7 @@
         <v>14</v>
       </c>
       <c r="E7" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>26</v>
@@ -1161,8 +1153,8 @@
       <c r="I7" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="J7" s="4" t="s">
-        <v>32</v>
+      <c r="J7" s="16">
+        <v>10</v>
       </c>
       <c r="K7" s="10" t="s">
         <v>27</v>
@@ -1174,7 +1166,7 @@
         <v>10</v>
       </c>
       <c r="V7" s="11" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.3">
@@ -1191,7 +1183,7 @@
         <v>14</v>
       </c>
       <c r="E8" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F8" s="4" t="s">
         <v>26</v>
@@ -1205,8 +1197,8 @@
       <c r="I8" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="J8" s="4" t="s">
-        <v>32</v>
+      <c r="J8" s="16">
+        <v>10</v>
       </c>
       <c r="K8" s="10" t="s">
         <v>25</v>
@@ -1218,10 +1210,10 @@
         <v>8</v>
       </c>
       <c r="N8" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="V8" s="11" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.3">
@@ -1238,7 +1230,7 @@
         <v>14</v>
       </c>
       <c r="E9" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F9" s="4" t="s">
         <v>34</v>
@@ -1252,8 +1244,8 @@
       <c r="I9" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="J9" s="4" t="s">
-        <v>37</v>
+      <c r="J9" s="16">
+        <v>12</v>
       </c>
       <c r="K9" s="10" t="s">
         <v>39</v>
@@ -1265,7 +1257,7 @@
         <v>10</v>
       </c>
       <c r="V9" s="11" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.3">
@@ -1282,7 +1274,7 @@
         <v>14</v>
       </c>
       <c r="E10" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F10" s="4" t="s">
         <v>34</v>
@@ -1296,8 +1288,8 @@
       <c r="I10" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="J10" s="4" t="s">
-        <v>37</v>
+      <c r="J10" s="16">
+        <v>12</v>
       </c>
       <c r="K10" s="10" t="s">
         <v>41</v>
@@ -1309,10 +1301,10 @@
         <v>8</v>
       </c>
       <c r="N10" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="V10" s="11" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.3">
@@ -1329,7 +1321,7 @@
         <v>14</v>
       </c>
       <c r="E11" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F11" s="4" t="s">
         <v>46</v>
@@ -1343,8 +1335,8 @@
       <c r="I11" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="J11" s="4" t="s">
-        <v>32</v>
+      <c r="J11" s="16">
+        <v>10</v>
       </c>
       <c r="K11" s="10" t="s">
         <v>44</v>
@@ -1357,7 +1349,7 @@
       </c>
       <c r="N11" s="4"/>
       <c r="V11" s="11" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.3">
@@ -1374,7 +1366,7 @@
         <v>14</v>
       </c>
       <c r="E12" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F12" s="4" t="s">
         <v>46</v>
@@ -1388,8 +1380,8 @@
       <c r="I12" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="J12" s="4" t="s">
-        <v>32</v>
+      <c r="J12" s="16">
+        <v>10</v>
       </c>
       <c r="K12" s="10" t="s">
         <v>45</v>
@@ -1402,7 +1394,7 @@
       </c>
       <c r="N12" s="4"/>
       <c r="V12" s="11" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.3">
@@ -1419,7 +1411,7 @@
         <v>49</v>
       </c>
       <c r="E13" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F13" s="4" t="s">
         <v>36</v>
@@ -1433,8 +1425,8 @@
       <c r="I13" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="J13" s="4" t="s">
-        <v>24</v>
+      <c r="J13" s="16">
+        <v>5</v>
       </c>
       <c r="K13" s="10" t="s">
         <v>52</v>
@@ -1446,10 +1438,10 @@
         <v>10</v>
       </c>
       <c r="N13" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="V13" s="11" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.3">
@@ -1480,8 +1472,8 @@
       <c r="I14" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="J14" s="4" t="s">
-        <v>24</v>
+      <c r="J14" s="16">
+        <v>5</v>
       </c>
       <c r="K14" s="10" t="s">
         <v>53</v>
@@ -1496,7 +1488,7 @@
         <v>54</v>
       </c>
       <c r="V14" s="11" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.3">
@@ -1513,7 +1505,7 @@
         <v>14</v>
       </c>
       <c r="E15" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F15" s="4" t="s">
         <v>17</v>
@@ -1527,8 +1519,8 @@
       <c r="I15" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="J15" s="4" t="s">
-        <v>56</v>
+      <c r="J15" s="16">
+        <v>7</v>
       </c>
       <c r="K15" s="10" t="s">
         <v>45</v>
@@ -1540,7 +1532,7 @@
         <v>8</v>
       </c>
       <c r="V15" s="11" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.3">
@@ -1557,7 +1549,7 @@
         <v>14</v>
       </c>
       <c r="E16" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F16" s="4" t="s">
         <v>17</v>
@@ -1571,8 +1563,8 @@
       <c r="I16" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="J16" s="4" t="s">
-        <v>56</v>
+      <c r="J16" s="16">
+        <v>7</v>
       </c>
       <c r="K16">
         <v>5.7</v>
@@ -1584,7 +1576,7 @@
         <v>10</v>
       </c>
       <c r="V16" s="11" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="17" spans="1:26" x14ac:dyDescent="0.3">
@@ -1615,8 +1607,8 @@
       <c r="I17" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="J17" s="4" t="s">
-        <v>59</v>
+      <c r="J17" s="16">
+        <v>13</v>
       </c>
       <c r="K17">
         <v>5</v>
@@ -1628,10 +1620,10 @@
         <v>10</v>
       </c>
       <c r="N17" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="V17" s="11" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="18" spans="1:26" x14ac:dyDescent="0.3">
@@ -1662,8 +1654,8 @@
       <c r="I18" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="J18" s="4" t="s">
-        <v>59</v>
+      <c r="J18" s="16">
+        <v>13</v>
       </c>
       <c r="K18">
         <v>6</v>
@@ -1675,7 +1667,7 @@
         <v>8</v>
       </c>
       <c r="V18" s="11" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="19" spans="1:26" x14ac:dyDescent="0.3">
@@ -1692,7 +1684,7 @@
         <v>14</v>
       </c>
       <c r="E19" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F19" s="4" t="s">
         <v>24</v>
@@ -1706,8 +1698,8 @@
       <c r="I19" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="J19" s="4" t="s">
-        <v>60</v>
+      <c r="J19" s="16">
+        <v>10</v>
       </c>
       <c r="K19">
         <v>5</v>
@@ -1719,10 +1711,10 @@
         <v>8</v>
       </c>
       <c r="N19" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="V19" s="11" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="20" spans="1:26" x14ac:dyDescent="0.3">
@@ -1739,7 +1731,7 @@
         <v>14</v>
       </c>
       <c r="E20" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F20" s="4" t="s">
         <v>24</v>
@@ -1753,8 +1745,8 @@
       <c r="I20" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="J20" s="4" t="s">
-        <v>60</v>
+      <c r="J20" s="16">
+        <v>10</v>
       </c>
       <c r="K20">
         <v>5.9</v>
@@ -1766,7 +1758,7 @@
         <v>10</v>
       </c>
       <c r="V20" s="11" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="21" spans="1:26" x14ac:dyDescent="0.3">
@@ -1786,7 +1778,7 @@
         <v>50</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G21" s="4" t="s">
         <v>46</v>
@@ -1797,8 +1789,8 @@
       <c r="I21" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="J21" s="4" t="s">
-        <v>60</v>
+      <c r="J21" s="16">
+        <v>10</v>
       </c>
       <c r="K21">
         <v>5</v>
@@ -1810,10 +1802,10 @@
         <v>8</v>
       </c>
       <c r="N21" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="V21" s="11" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="22" spans="1:26" x14ac:dyDescent="0.3">
@@ -1833,7 +1825,7 @@
         <v>50</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G22" s="4" t="s">
         <v>46</v>
@@ -1844,8 +1836,8 @@
       <c r="I22" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="J22" s="4" t="s">
-        <v>60</v>
+      <c r="J22" s="16">
+        <v>10</v>
       </c>
       <c r="K22">
         <v>6.6</v>
@@ -1857,10 +1849,10 @@
         <v>10</v>
       </c>
       <c r="V22" s="11" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="Z22" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="23" spans="1:26" x14ac:dyDescent="0.3">
@@ -1891,8 +1883,8 @@
       <c r="I23" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="J23" s="4" t="s">
-        <v>60</v>
+      <c r="J23" s="16">
+        <v>10</v>
       </c>
       <c r="K23">
         <v>5.4</v>
@@ -1904,10 +1896,10 @@
         <v>8</v>
       </c>
       <c r="N23" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="V23" s="11" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="24" spans="1:26" x14ac:dyDescent="0.3">
@@ -1938,8 +1930,8 @@
       <c r="I24" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="J24" s="4" t="s">
-        <v>60</v>
+      <c r="J24" s="16">
+        <v>10</v>
       </c>
       <c r="K24">
         <v>6.3</v>
@@ -1954,7 +1946,7 @@
         <v>1</v>
       </c>
       <c r="V24" s="11" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="25" spans="1:26" x14ac:dyDescent="0.3">
@@ -1985,8 +1977,8 @@
       <c r="I25" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="J25" s="4" t="s">
-        <v>56</v>
+      <c r="J25" s="16">
+        <v>7</v>
       </c>
       <c r="K25" s="10">
         <v>4.7</v>
@@ -1998,10 +1990,10 @@
         <v>8</v>
       </c>
       <c r="N25" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="V25" s="11" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="26" spans="1:26" x14ac:dyDescent="0.3">
@@ -2032,8 +2024,8 @@
       <c r="I26" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="J26" s="4" t="s">
-        <v>59</v>
+      <c r="J26" s="16">
+        <v>12</v>
       </c>
       <c r="K26">
         <v>5.7</v>
@@ -2045,7 +2037,7 @@
         <v>10</v>
       </c>
       <c r="V26" s="11" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="27" spans="1:26" x14ac:dyDescent="0.3">
@@ -2062,7 +2054,7 @@
         <v>14</v>
       </c>
       <c r="E27" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F27" s="4" t="s">
         <v>57</v>
@@ -2076,8 +2068,8 @@
       <c r="I27">
         <v>0</v>
       </c>
-      <c r="J27" s="4" t="s">
-        <v>60</v>
+      <c r="J27" s="16">
+        <v>10</v>
       </c>
       <c r="K27" s="10">
         <v>5</v>
@@ -2092,7 +2084,7 @@
         <v>1</v>
       </c>
       <c r="V27" s="11" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="28" spans="1:26" x14ac:dyDescent="0.3">
@@ -2109,7 +2101,7 @@
         <v>14</v>
       </c>
       <c r="E28" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F28" s="4" t="s">
         <v>57</v>
@@ -2123,8 +2115,8 @@
       <c r="I28">
         <v>0</v>
       </c>
-      <c r="J28" s="4" t="s">
-        <v>60</v>
+      <c r="J28" s="16">
+        <v>10</v>
       </c>
       <c r="K28" s="10">
         <v>5.8</v>
@@ -2136,10 +2128,10 @@
         <v>8</v>
       </c>
       <c r="N28" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="V28" s="11" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="29" spans="1:26" x14ac:dyDescent="0.3">
@@ -2156,10 +2148,10 @@
         <v>14</v>
       </c>
       <c r="E29" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G29" s="4" t="s">
         <v>46</v>
@@ -2170,8 +2162,8 @@
       <c r="I29">
         <v>0</v>
       </c>
-      <c r="J29" s="4" t="s">
-        <v>60</v>
+      <c r="J29" s="16">
+        <v>10</v>
       </c>
       <c r="K29" s="15"/>
       <c r="L29">
@@ -2181,7 +2173,7 @@
         <v>10</v>
       </c>
       <c r="V29" s="11" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="30" spans="1:26" x14ac:dyDescent="0.3">
@@ -2198,10 +2190,10 @@
         <v>14</v>
       </c>
       <c r="E30" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G30" s="4" t="s">
         <v>46</v>
@@ -2212,8 +2204,8 @@
       <c r="I30">
         <v>0</v>
       </c>
-      <c r="J30" s="4" t="s">
-        <v>60</v>
+      <c r="J30" s="16">
+        <v>10</v>
       </c>
       <c r="K30" s="15"/>
       <c r="L30">
@@ -2223,7 +2215,7 @@
         <v>8</v>
       </c>
       <c r="V30" s="11" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="31" spans="1:26" x14ac:dyDescent="0.3">
@@ -2240,7 +2232,7 @@
         <v>14</v>
       </c>
       <c r="E31" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F31" s="4" t="s">
         <v>24</v>
@@ -2254,8 +2246,8 @@
       <c r="I31">
         <v>0</v>
       </c>
-      <c r="J31" s="4" t="s">
-        <v>66</v>
+      <c r="J31" s="16">
+        <v>15</v>
       </c>
       <c r="K31" s="15"/>
       <c r="L31">
@@ -2265,7 +2257,7 @@
         <v>10</v>
       </c>
       <c r="V31" s="11" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="32" spans="1:26" x14ac:dyDescent="0.3">
@@ -2282,7 +2274,7 @@
         <v>14</v>
       </c>
       <c r="E32" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F32" s="4" t="s">
         <v>24</v>
@@ -2296,8 +2288,8 @@
       <c r="I32">
         <v>0</v>
       </c>
-      <c r="J32" s="4" t="s">
-        <v>66</v>
+      <c r="J32" s="16">
+        <v>15</v>
       </c>
       <c r="K32" s="15"/>
       <c r="L32">
@@ -2307,7 +2299,7 @@
         <v>8</v>
       </c>
       <c r="V32" s="11" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="33" spans="1:22" x14ac:dyDescent="0.3">
@@ -2315,7 +2307,7 @@
         <v>45630</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C33" s="3">
         <v>0.45347222222222222</v>
@@ -2324,10 +2316,10 @@
         <v>49</v>
       </c>
       <c r="E33" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G33" s="4" t="s">
         <v>18</v>
@@ -2338,8 +2330,8 @@
       <c r="I33">
         <v>8</v>
       </c>
-      <c r="J33" s="4" t="s">
-        <v>24</v>
+      <c r="J33" s="16">
+        <v>5</v>
       </c>
       <c r="K33" s="15"/>
       <c r="L33">
@@ -2349,7 +2341,7 @@
         <v>10</v>
       </c>
       <c r="V33" s="11" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="34" spans="1:22" x14ac:dyDescent="0.3">
@@ -2357,7 +2349,7 @@
         <v>45631</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C34" s="3">
         <v>0.47222222222222221</v>
@@ -2366,7 +2358,7 @@
         <v>49</v>
       </c>
       <c r="E34" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F34" s="4" t="s">
         <v>24</v>
@@ -2380,8 +2372,8 @@
       <c r="I34">
         <v>0</v>
       </c>
-      <c r="J34" s="4" t="s">
-        <v>24</v>
+      <c r="J34" s="16">
+        <v>5</v>
       </c>
       <c r="K34" s="15"/>
       <c r="L34">
@@ -2391,7 +2383,7 @@
         <v>10</v>
       </c>
       <c r="V34" s="11" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="35" spans="1:22" x14ac:dyDescent="0.3">
@@ -2399,7 +2391,7 @@
         <v>45632</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C35" s="3">
         <v>0.5</v>
@@ -2408,7 +2400,7 @@
         <v>49</v>
       </c>
       <c r="E35" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F35" s="4" t="s">
         <v>58</v>
@@ -2422,8 +2414,8 @@
       <c r="I35">
         <v>2</v>
       </c>
-      <c r="J35" s="4" t="s">
-        <v>24</v>
+      <c r="J35" s="16">
+        <v>5</v>
       </c>
       <c r="K35" s="15"/>
       <c r="L35">
@@ -2433,10 +2425,10 @@
         <v>10</v>
       </c>
       <c r="O35" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="V35" s="11" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="36" spans="1:22" x14ac:dyDescent="0.3">
@@ -2444,7 +2436,7 @@
         <v>45634</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C36" s="3">
         <v>0.54861111111111116</v>
@@ -2453,7 +2445,7 @@
         <v>49</v>
       </c>
       <c r="E36" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F36" s="4"/>
       <c r="G36" s="4"/>
@@ -2463,6 +2455,9 @@
       <c r="I36">
         <v>3</v>
       </c>
+      <c r="J36" s="16">
+        <v>5</v>
+      </c>
       <c r="K36" s="15"/>
       <c r="L36">
         <v>29</v>
@@ -2471,7 +2466,7 @@
         <v>10</v>
       </c>
       <c r="V36" s="11" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="37" spans="1:22" x14ac:dyDescent="0.3">
@@ -2488,19 +2483,22 @@
         <v>14</v>
       </c>
       <c r="E37" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F37" s="4" t="s">
         <v>46</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H37">
         <v>3</v>
       </c>
       <c r="I37">
         <v>3</v>
+      </c>
+      <c r="J37" s="16">
+        <v>17</v>
       </c>
       <c r="K37" s="15"/>
       <c r="L37">
@@ -2510,7 +2508,7 @@
         <v>10</v>
       </c>
       <c r="V37" s="11" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="38" spans="1:22" x14ac:dyDescent="0.3">
@@ -2518,7 +2516,7 @@
         <v>45635</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C38" s="3">
         <v>0.38819444444444445</v>
@@ -2527,10 +2525,10 @@
         <v>49</v>
       </c>
       <c r="E38" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G38" s="4" t="s">
         <v>46</v>
@@ -2540,6 +2538,9 @@
       </c>
       <c r="I38">
         <v>0</v>
+      </c>
+      <c r="J38" s="16">
+        <v>6</v>
       </c>
       <c r="K38" s="15"/>
       <c r="L38">
@@ -2549,7 +2550,7 @@
         <v>10</v>
       </c>
       <c r="V38" s="11" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="39" spans="1:22" x14ac:dyDescent="0.3">
@@ -2566,7 +2567,7 @@
         <v>14</v>
       </c>
       <c r="E39" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F39" s="4" t="s">
         <v>24</v>
@@ -2580,8 +2581,8 @@
       <c r="I39">
         <v>6</v>
       </c>
-      <c r="J39" s="4" t="s">
-        <v>66</v>
+      <c r="J39" s="16">
+        <v>15</v>
       </c>
       <c r="K39" s="15"/>
       <c r="L39">
@@ -2591,7 +2592,7 @@
         <v>10</v>
       </c>
       <c r="V39" s="11" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="40" spans="1:22" x14ac:dyDescent="0.3">
@@ -2608,7 +2609,7 @@
         <v>14</v>
       </c>
       <c r="E40" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F40" s="4" t="s">
         <v>24</v>
@@ -2622,8 +2623,8 @@
       <c r="I40">
         <v>6</v>
       </c>
-      <c r="J40" s="4" t="s">
-        <v>66</v>
+      <c r="J40" s="16">
+        <v>15</v>
       </c>
       <c r="K40" s="15"/>
       <c r="L40">
@@ -2633,7 +2634,7 @@
         <v>8</v>
       </c>
       <c r="V40" s="11" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="41" spans="1:22" x14ac:dyDescent="0.3">
@@ -2641,7 +2642,7 @@
         <v>45636</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C41" s="3">
         <v>0.67222222222222228</v>
@@ -2650,7 +2651,7 @@
         <v>49</v>
       </c>
       <c r="E41" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F41" s="4" t="s">
         <v>24</v>
@@ -2664,8 +2665,8 @@
       <c r="I41">
         <v>0</v>
       </c>
-      <c r="J41" s="4" t="s">
-        <v>24</v>
+      <c r="J41" s="16">
+        <v>5</v>
       </c>
       <c r="K41" s="15"/>
       <c r="L41">
@@ -2675,7 +2676,7 @@
         <v>10</v>
       </c>
       <c r="V41" s="11" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="42" spans="1:22" x14ac:dyDescent="0.3">
@@ -2698,7 +2699,7 @@
         <v>18</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H42">
         <v>0</v>
@@ -2706,8 +2707,8 @@
       <c r="I42">
         <v>0</v>
       </c>
-      <c r="J42" s="4" t="s">
-        <v>128</v>
+      <c r="J42" s="16">
+        <v>20</v>
       </c>
       <c r="K42" s="10">
         <v>5.8</v>
@@ -2719,7 +2720,7 @@
         <v>9</v>
       </c>
       <c r="V42" s="11" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="43" spans="1:22" x14ac:dyDescent="0.3">
@@ -2730,7 +2731,7 @@
         <v>6</v>
       </c>
       <c r="C43" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D43" t="s">
         <v>14</v>
@@ -2742,7 +2743,7 @@
         <v>36</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H43">
         <v>0</v>
@@ -2750,8 +2751,8 @@
       <c r="I43">
         <v>0</v>
       </c>
-      <c r="J43" s="4" t="s">
-        <v>66</v>
+      <c r="J43" s="16">
+        <v>15</v>
       </c>
       <c r="K43" s="10">
         <v>5.9</v>
@@ -2763,7 +2764,7 @@
         <v>9</v>
       </c>
       <c r="V43" s="11" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="44" spans="1:22" x14ac:dyDescent="0.3">
@@ -2771,10 +2772,10 @@
         <v>45345</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C44" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D44" t="s">
         <v>14</v>
@@ -2794,8 +2795,8 @@
       <c r="I44">
         <v>0</v>
       </c>
-      <c r="J44" s="4" t="s">
-        <v>46</v>
+      <c r="J44" s="16">
+        <v>6</v>
       </c>
       <c r="K44" s="10">
         <v>5.2</v>
@@ -2804,7 +2805,7 @@
         <v>8</v>
       </c>
       <c r="V44" s="11" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="45" spans="1:22" x14ac:dyDescent="0.3">
@@ -2812,10 +2813,10 @@
         <v>46003</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C45" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D45" t="s">
         <v>14</v>
@@ -2835,8 +2836,8 @@
       <c r="I45">
         <v>0</v>
       </c>
-      <c r="J45" s="4" t="s">
-        <v>24</v>
+      <c r="J45" s="16">
+        <v>5</v>
       </c>
       <c r="K45" s="10">
         <v>5.2</v>
@@ -2848,7 +2849,7 @@
         <v>8</v>
       </c>
       <c r="V45" s="11" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="46" spans="1:22" x14ac:dyDescent="0.3">
@@ -2856,10 +2857,10 @@
         <v>45622</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C46" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D46" t="s">
         <v>14</v>
@@ -2879,8 +2880,8 @@
       <c r="I46">
         <v>0</v>
       </c>
-      <c r="J46" s="4" t="s">
-        <v>46</v>
+      <c r="J46" s="16">
+        <v>6</v>
       </c>
       <c r="K46" s="10">
         <v>5</v>
@@ -2892,7 +2893,7 @@
         <v>9</v>
       </c>
       <c r="V46" s="11" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="47" spans="1:22" x14ac:dyDescent="0.3">
@@ -2900,10 +2901,10 @@
         <v>45299</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C47" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D47" t="s">
         <v>49</v>
@@ -2923,8 +2924,8 @@
       <c r="I47">
         <v>2</v>
       </c>
-      <c r="J47" s="4" t="s">
-        <v>24</v>
+      <c r="J47" s="16">
+        <v>5</v>
       </c>
       <c r="K47" s="10">
         <v>3.8</v>
@@ -2933,10 +2934,10 @@
         <v>8</v>
       </c>
       <c r="N47" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="V47" s="11" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="48" spans="1:22" x14ac:dyDescent="0.3">
@@ -2944,10 +2945,10 @@
         <v>45297</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C48" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D48" t="s">
         <v>49</v>
@@ -2967,8 +2968,8 @@
       <c r="I48">
         <v>0</v>
       </c>
-      <c r="J48" s="4" t="s">
-        <v>46</v>
+      <c r="J48" s="16">
+        <v>6</v>
       </c>
       <c r="K48" s="10">
         <v>4</v>
@@ -2977,115 +2978,115 @@
         <v>8</v>
       </c>
       <c r="N48" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="V48" s="11" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="57" spans="1:22" x14ac:dyDescent="0.3">
       <c r="T57" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V57" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="58" spans="1:22" x14ac:dyDescent="0.3">
       <c r="T58" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="V58" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="59" spans="1:22" x14ac:dyDescent="0.3">
       <c r="V59" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="60" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B60" t="s">
+        <v>70</v>
+      </c>
+      <c r="D60" t="s">
         <v>71</v>
-      </c>
-      <c r="B60" t="s">
-        <v>72</v>
-      </c>
-      <c r="D60" t="s">
-        <v>73</v>
       </c>
       <c r="F60" s="4"/>
       <c r="G60" s="4"/>
       <c r="V60" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="61" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A61" s="2"/>
       <c r="D61" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F61" s="4"/>
       <c r="G61" s="4"/>
       <c r="H61" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="V61" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="62" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A62" s="2"/>
       <c r="D62" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F62" s="4"/>
       <c r="G62" s="4"/>
       <c r="H62" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="V62" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="63" spans="1:22" x14ac:dyDescent="0.3">
       <c r="V63" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="64" spans="1:22" x14ac:dyDescent="0.3">
       <c r="V64" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="65" spans="1:22" x14ac:dyDescent="0.3">
       <c r="V65" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="66" spans="1:22" x14ac:dyDescent="0.3">
       <c r="V66" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="67" spans="1:22" x14ac:dyDescent="0.3">
       <c r="V67" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="68" spans="1:22" x14ac:dyDescent="0.3">
       <c r="V68" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="69" spans="1:22" x14ac:dyDescent="0.3">
       <c r="V69" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="70" spans="1:22" x14ac:dyDescent="0.3">
       <c r="V70" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="71" spans="1:22" x14ac:dyDescent="0.3">
@@ -3116,7 +3117,7 @@
       <c r="I71" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="J71" s="4">
+      <c r="J71" s="16">
         <v>6</v>
       </c>
       <c r="K71" s="10" t="s">
@@ -3129,7 +3130,7 @@
         <v>31</v>
       </c>
       <c r="V71" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="72" spans="1:22" x14ac:dyDescent="0.3">
@@ -3160,7 +3161,7 @@
       <c r="I72" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="J72" s="4" t="s">
+      <c r="J72" s="16" t="s">
         <v>37</v>
       </c>
       <c r="K72" s="10" t="s">
@@ -3176,7 +3177,7 @@
         <v>38</v>
       </c>
       <c r="V72" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="73" spans="1:22" x14ac:dyDescent="0.3">
@@ -3207,7 +3208,7 @@
       <c r="I73" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="J73" s="4" t="s">
+      <c r="J73" s="16" t="s">
         <v>32</v>
       </c>
       <c r="K73" s="10" t="s">
@@ -3251,11 +3252,11 @@
       <c r="I74" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="J74" s="4" t="s">
+      <c r="J74" s="16" t="s">
         <v>56</v>
       </c>
       <c r="K74" s="10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="L74">
         <v>28</v>
@@ -3269,7 +3270,7 @@
         <v>45622</v>
       </c>
       <c r="B75" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D75" t="s">
         <v>14</v>
@@ -3286,7 +3287,7 @@
         <v>45622</v>
       </c>
       <c r="B76" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D76" t="s">
         <v>14</v>
@@ -3300,79 +3301,79 @@
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83" s="13" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D83" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="G83" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A84" s="13" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D84" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G84" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A85" s="12" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E85" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G85" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A86" s="14" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E86" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="G86" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87" s="14" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E87" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G87" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A88" s="14" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E88" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G88" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A89" s="14" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E89" t="s">
+        <v>105</v>
+      </c>
+      <c r="G89" t="s">
         <v>107</v>
-      </c>
-      <c r="G89" t="s">
-        <v>109</v>
       </c>
     </row>
   </sheetData>
